--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios133.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios133.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4218006815297</v>
+        <v>27.42240646791319</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.57433618391669</v>
+        <v>28.7456413624982</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.29478231042926</v>
+        <v>30.2607603453244</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.42170299983783</v>
+        <v>24.98402813468936</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.42562060773347</v>
+        <v>30.00971045307836</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.47851571761272</v>
+        <v>23.47254553119873</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.33623751041223</v>
+        <v>27.88548298121171</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.97314759768165</v>
+        <v>28.51514376506153</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31.24710171783331</v>
+        <v>30.74461115969297</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.17082064563153</v>
+        <v>24.85689026183812</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30.06345979949946</v>
+        <v>29.93516601361679</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20.6595946665824</v>
+        <v>23.10852507399628</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26.45733108825153</v>
+        <v>27.69271275583195</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.62161694059622</v>
+        <v>28.61290945898136</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31.81881676839676</v>
+        <v>30.11434150046437</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.26243770879548</v>
+        <v>25.21421374565169</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.99813667415015</v>
+        <v>30.018454691501</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.56853000622619</v>
+        <v>23.60548604240009</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.70400346885862</v>
+        <v>32.438964321973</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.57423408461178</v>
+        <v>24.00026768882566</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.33059991720743</v>
+        <v>23.90184267503455</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.96212221277759</v>
+        <v>29.1889083482144</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.29149387066097</v>
+        <v>34.89426180282094</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.10493825262535</v>
+        <v>25.85883016618633</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>27.28989434103833</v>
+        <v>32.67429925060151</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>28.25802211203591</v>
+        <v>24.05055203864849</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21.27313994834424</v>
+        <v>23.86701654073049</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.70443304779572</v>
+        <v>29.26220275213662</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.4272006435972</v>
+        <v>34.66543687784625</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.19958812039205</v>
+        <v>26.11431162259944</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.40154399453787</v>
+        <v>32.24604016641307</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.5946892676984</v>
+        <v>24.16253125907671</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>21.58891702561983</v>
+        <v>23.81063908955559</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.86453455410322</v>
+        <v>28.64046447153377</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.29999056640506</v>
+        <v>34.74101992837006</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.2447870926051</v>
+        <v>25.56824694451892</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.24528641936691</v>
+        <v>27.62017297968148</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>33.7056274889384</v>
+        <v>33.05012981028315</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25.26760610870734</v>
+        <v>20.2619352084646</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.24420071282895</v>
+        <v>21.43060445240444</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>32.49589686047381</v>
+        <v>31.17838081489567</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>21.17520446177121</v>
+        <v>23.45923973545624</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.28006027081649</v>
+        <v>26.95609163461875</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>32.52677676539652</v>
+        <v>33.5202087615252</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.89036176615701</v>
+        <v>20.51267769707152</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25.12782470659361</v>
+        <v>21.93627747737159</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.94747197654592</v>
+        <v>31.01718600294622</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>21.12863585765485</v>
+        <v>24.03051776625603</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27.0346954821531</v>
+        <v>27.3889346399654</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33.01986392290021</v>
+        <v>32.88188383558592</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>26.18488351398837</v>
+        <v>20.65872862292209</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>25.12072344766357</v>
+        <v>22.03498857876727</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.29563412837216</v>
+        <v>31.25083727512822</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>21.3477211455508</v>
+        <v>24.04845241535074</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios133.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios133.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.42240646791319</v>
+        <v>27.33250073627249</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.7456413624982</v>
+        <v>27.51020176042679</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.2607603453244</v>
+        <v>23.6188793761736</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.98402813468936</v>
+        <v>28.28188224044073</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.00971045307836</v>
+        <v>36.69948546929047</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.47254553119873</v>
+        <v>18.87722137123148</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.88548298121171</v>
+        <v>26.546737783977</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.51514376506153</v>
+        <v>27.30554250579514</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.74461115969297</v>
+        <v>24.22881986172537</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.85689026183812</v>
+        <v>28.47364376756971</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.93516601361679</v>
+        <v>36.50053848706962</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.10852507399628</v>
+        <v>18.65505492564156</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.69271275583195</v>
+        <v>26.63171717925212</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.61290945898136</v>
+        <v>27.15830789052816</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30.11434150046437</v>
+        <v>24.53268166772946</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.21421374565169</v>
+        <v>28.34357088016423</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.018454691501</v>
+        <v>36.47815503832553</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23.60548604240009</v>
+        <v>18.88946808017817</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32.438964321973</v>
+        <v>31.64781403737697</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.00026768882566</v>
+        <v>23.7268637864833</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.90184267503455</v>
+        <v>23.79239405728459</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.1889083482144</v>
+        <v>30.89871153558992</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34.89426180282094</v>
+        <v>30.57535651422823</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.85883016618633</v>
+        <v>21.64254610078658</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.67429925060151</v>
+        <v>31.12769487880079</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24.05055203864849</v>
+        <v>23.66631368592397</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23.86701654073049</v>
+        <v>23.93552427386036</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.26220275213662</v>
+        <v>31.03057960699481</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34.66543687784625</v>
+        <v>29.21420939347027</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.11431162259944</v>
+        <v>21.5735116881387</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32.24604016641307</v>
+        <v>30.91188329162</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>24.16253125907671</v>
+        <v>23.19136122247685</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>23.81063908955559</v>
+        <v>24.55384757285983</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.64046447153377</v>
+        <v>30.60501619307586</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>34.74101992837006</v>
+        <v>30.05997812923706</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.56824694451892</v>
+        <v>21.82529262216718</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.62017297968148</v>
+        <v>27.3136910012132</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>33.05012981028315</v>
+        <v>29.47350965148663</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20.2619352084646</v>
+        <v>23.42086080818338</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.43060445240444</v>
+        <v>28.60901132886577</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>31.17838081489567</v>
+        <v>29.84092104974376</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>23.45923973545624</v>
+        <v>23.56716238305183</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>26.95609163461875</v>
+        <v>26.97921729884278</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>33.5202087615252</v>
+        <v>29.72339160233211</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20.51267769707152</v>
+        <v>23.16773041496623</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>21.93627747737159</v>
+        <v>28.49586091945199</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31.01718600294622</v>
+        <v>30.17092591911533</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24.03051776625603</v>
+        <v>23.61408628118333</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27.3889346399654</v>
+        <v>27.35266409219366</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>32.88188383558592</v>
+        <v>29.5327312918008</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20.65872862292209</v>
+        <v>23.64540085406747</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>22.03498857876727</v>
+        <v>28.04766817415214</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31.25083727512822</v>
+        <v>30.09097247741924</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.04845241535074</v>
+        <v>23.59677055786964</v>
       </c>
     </row>
   </sheetData>
